--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_950_Nicaragua_Pacific.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_950_Nicaragua_Pacific.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R91c3495f000c47af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rba370d2280ca4921"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rebd7538f8b054076"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Re534e648f287490c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R637f2710f8cc4fe5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R163f8dfb25ba4415"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rd83b747b2ddf4cef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R4f6cc547cd1f4493"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rcdd11e9f14374ca5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R6dd55dcbf857456a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Reac8a1b9a28b44b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rf4ee1c74da1a42bb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ950CommercialTable" displayName="EEZ950CommercialTable" ref="A1:O9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O9"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ950CommercialTable" displayName="EEZ950CommercialTable" ref="A1:E9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E9"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ950FunctionalTable" displayName="EEZ950FunctionalTable" ref="A1:O14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O14"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ950FunctionalTable" displayName="EEZ950FunctionalTable" ref="A1:E14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E14"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ950ValidationTable" displayName="EEZ950ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ950ValidationTable" displayName="EEZ950ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -3776,7 +3730,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd94e89a4954f46d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f5adf909e054b6c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3786,20 +3740,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -3807,498 +3751,174 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>6207.973777965901</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.795045182390144</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>62.37997299212735</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>6207.973777965901</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>68.33669708529325</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$47,A2,'Species'!$U$2:$U$47))</x:f>
-        <x:v>424232.42357829935</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.795045182390144</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>62.37997299212735</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>387253.23660534766</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>36979.18697295169</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0954909694160604</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.09549096941606049</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>588.3391341134</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.5700000000000003</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>371.53522909717276</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>588.3391341134</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$47,A3,'Species'!$U$2:$U$47))</x:f>
-        <x:v>218588.7149796541</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.5700000000000003</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>371.53522909717276</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>218588.7149796543</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>-2.0372681319713593e-10</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>0.9999999999999991</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>-9.320097481523615e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>373.0668276954</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.16</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>144.5439770745928</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>373.0668276954</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$47,A4,'Species'!$U$2:$U$47))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>53924.562989694954</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.16</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>53924.562989694954</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>966.4010829325001</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>966.4010829325001</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$47,A5,'Species'!$U$2:$U$47))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>12166.26881289127</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>12166.26881289127</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1540.9677251905</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.3039088212239345</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>201.33015190947305</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1540.9677251905</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>212.83048320665588</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$47,A6,'Species'!$U$2:$U$47))</x:f>
-        <x:v>327964.90555815544</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.3039088212239345</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>201.33015190947305</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>310243.2662001985</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>17721.63935795694</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0571217534388684</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.05712175343886836</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>6860.779808884099</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.9254815406112007</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>842.3285880791517</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>6860.779808884099</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1040.8305589424842</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$47,A7,'Species'!$U$2:$U$47))</x:f>
-        <x:v>7140909.283262147</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.9254815406112007</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>842.3285880791517</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>5779030.969539296</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1361878.3137228508</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.2356585941312959</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.23565859413129597</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>446.94828149200004</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.841945980870638</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>694.9378733091313</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>446.94828149200004</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>845.0272959872366</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$47,A8,'Species'!$U$2:$U$47))</x:f>
-        <x:v>377683.49775532703</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.841945980870638</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>694.9378733091313</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>310601.28821922146</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>67082.20953610557</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.215975310085511</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.21597531008551113</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>7571.869355794798</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.410704731623636</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2574.57016162816</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>7571.869355794798</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2579.317826586623</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$47,A9,'Species'!$U$2:$U$47))</x:f>
-        <x:v>19530257.60998649</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.410704731623636</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2574.57016162816</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>19494308.911175925</x:v>
       </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>35948.69881056622</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.001844061206497</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0018440612064968933</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G9">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O9">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04073c63baa044d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae756844135d4595"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4308,20 +3928,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4329,768 +3939,269 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>12.219999999999999</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.6284615384615386</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>425.07106043428644</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>12.219999999999999</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>453.75465467259596</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$47,A2,'Species'!$U$2:$U$47))</x:f>
-        <x:v>5544.881880099122</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.6284615384615386</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>425.07106043428644</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>5194.368358506979</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>350.51352159214275</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.06747952732657</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.06747952732657009</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>52.8639300663</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.89</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>776.247116628692</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>52.8639300663</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>776.247116628692</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$47,A3,'Species'!$U$2:$U$47))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>41035.47328762619</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.89</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>776.247116628692</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>41035.47328762619</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>7973.328523720398</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.415539839314091</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2603.393638598685</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>7973.328523720398</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2607.106370351021</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$47,A4,'Species'!$U$2:$U$47))</x:f>
-        <x:v>20787315.58709295</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.415539839314091</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2603.393638598685</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>20757712.75711113</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>29602.82998182252</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.001426112324041</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0014261123240411568</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>311.5066611445</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.676184564561627</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>474.44356936754104</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>311.5066611445</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>478.03361360288295</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$47,A5,'Species'!$U$2:$U$47))</x:f>
-        <x:v>148910.65488827412</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.676184564561627</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>474.44356936754104</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>147792.3321951617</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1118.3226931124227</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.007566851923249</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0075668519232490565</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>135.44162034750005</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.223186143300195</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1671.8070152936712</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>135.44162034750005</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1689.0882011016608</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$47,A6,'Species'!$U$2:$U$47))</x:f>
-        <x:v>228772.84286705297</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.223186143300195</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1671.8070152936712</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>226432.25105969261</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2340.5918073603534</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0103368305371982</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.01033683053719817</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1666.6200000000001</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.0540327129159617</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>113.24856636818137</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1666.6200000000001</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>117.97864533495938</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$47,A7,'Species'!$U$2:$U$47))</x:f>
-        <x:v>196625.56988815003</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.0540327129159617</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>113.24856636818137</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>188742.32568053846</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>7883.244207611569</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0417672304247994</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.04176723042479933</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>3035.0913696386006</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.3974096661161877</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>249.69489661194808</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>3035.0913696386006</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>319.0862321199204</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$47,A8,'Species'!$U$2:$U$47))</x:f>
-        <x:v>968455.8692776696</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.3974096661161877</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>249.69489661194808</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>757846.8257497263</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>210609.04352794331</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.2779045004504586</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.27790450045045845</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>171.74115620589998</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.196639349015456</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1572.6763251054688</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>171.74115620589998</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1674.1646281169435</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$47,A9,'Species'!$U$2:$U$47))</x:f>
-        <x:v>287522.96891182446</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.196639349015456</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1572.6763251054688</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>270093.25041125907</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>17429.71850056539</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0645322253481933</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.06453222534819336</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>4728.371910238199</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.003840438434853</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1008.8821505562959</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>4728.371910238199</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1038.2552623931208</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$47,A10,'Species'!$U$2:$U$47))</x:f>
-        <x:v>4909257.018356623</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.003840438434853</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1008.8821505562959</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>4770370.021431095</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>138886.99692552816</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0291145123547172</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0291145123547172</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>966.4010829325001</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>966.4010829325001</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$47,A11,'Species'!$U$2:$U$47))</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>12166.26881289127</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>12166.26881289127</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>4541.3537779659</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.700000000000001</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>50.11872336272735</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>4541.3537779659</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>50.11872336272725</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$47,A12,'Species'!$U$2:$U$47))</x:f>
-        <x:v>227606.85369014923</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.700000000000001</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>50.11872336272735</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>227606.85369014967</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>-4.3655745685100555e-10</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>0.9999999999999981</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>-1.9180330019644695e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>373.0668276954</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.16</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>144.5439770745928</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>373.0668276954</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$47,A13,'Species'!$U$2:$U$47))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>53924.562989694954</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.16</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>53924.562989694954</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>588.3391341134</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.5700000000000003</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>371.53522909717276</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>588.3391341134</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$47,A14,'Species'!$U$2:$U$47))</x:f>
-        <x:v>218588.7149796541</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.5700000000000003</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>371.53522909717276</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>218588.7149796543</x:v>
       </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>-2.0372681319713593e-10</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>0.9999999999999991</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>-9.320097481523615e-16</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G14">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O14">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1697d7ec205741a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R993e8cc30fb04304"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5265,7 +4376,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -5364,7 +4475,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>28085727.26692266</x:v>
+        <x:v>26566117.21852223</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5378,7 +4489,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>28085727.266922656</x:v>
+        <x:v>27677506.00575713</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5392,7 +4503,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-7.450580596923828e-9</x:v>
+        <x:v>-1519610.0484004393</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5406,7 +4517,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-1.1175870895385742e-8</x:v>
+        <x:v>-408221.26116553694</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5417,9 +4528,9 @@
         <x:v>EEZ_950</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -5431,47 +4542,19 @@
         <x:v>EEZ_950</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_950</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_950</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0d17b2ecdaf4df5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b9928c7bb0a475e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5518,7 +4601,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
